--- a/product/dist/svatebni-planovac-demo.xlsx
+++ b/product/dist/svatebni-planovac-demo.xlsx
@@ -6187,7 +6187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M254"/>
+  <dimension ref="A1:O254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6203,6 +6203,8 @@
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -6285,6 +6287,16 @@
           <t>Poznámka</t>
         </is>
       </c>
+      <c r="N4" s="22" t="inlineStr">
+        <is>
+          <t>Dar (po svatbě)</t>
+        </is>
+      </c>
+      <c r="O4" s="23" t="inlineStr">
+        <is>
+          <t>Poděkováno</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
@@ -6338,6 +6350,16 @@
       </c>
       <c r="L5" s="24" t="n"/>
       <c r="M5" s="24" t="n"/>
+      <c r="N5" s="24" t="inlineStr">
+        <is>
+          <t>Příspěvek na cestu</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="24" t="inlineStr">
@@ -6391,6 +6413,16 @@
       </c>
       <c r="L6" s="24" t="n"/>
       <c r="M6" s="24" t="n"/>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
+          <t>Sada nádobí</t>
+        </is>
+      </c>
+      <c r="O6" s="27" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
@@ -6444,6 +6476,16 @@
       </c>
       <c r="L7" s="24" t="n"/>
       <c r="M7" s="24" t="n"/>
+      <c r="N7" s="24" t="inlineStr">
+        <is>
+          <t>Obraz</t>
+        </is>
+      </c>
+      <c r="O7" s="27" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
@@ -6497,6 +6539,8 @@
       </c>
       <c r="L8" s="24" t="n"/>
       <c r="M8" s="24" t="n"/>
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
@@ -6550,6 +6594,8 @@
       </c>
       <c r="L9" s="24" t="n"/>
       <c r="M9" s="24" t="n"/>
+      <c r="N9" s="24" t="n"/>
+      <c r="O9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
@@ -6603,6 +6649,8 @@
       </c>
       <c r="L10" s="24" t="n"/>
       <c r="M10" s="24" t="n"/>
+      <c r="N10" s="24" t="n"/>
+      <c r="O10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
@@ -6656,6 +6704,8 @@
       </c>
       <c r="L11" s="24" t="n"/>
       <c r="M11" s="24" t="n"/>
+      <c r="N11" s="24" t="n"/>
+      <c r="O11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
@@ -6705,6 +6755,8 @@
       </c>
       <c r="L12" s="24" t="n"/>
       <c r="M12" s="24" t="n"/>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
@@ -6758,6 +6810,8 @@
       </c>
       <c r="L13" s="24" t="n"/>
       <c r="M13" s="24" t="n"/>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="27" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
@@ -6811,6 +6865,8 @@
       </c>
       <c r="L14" s="24" t="n"/>
       <c r="M14" s="24" t="n"/>
+      <c r="N14" s="24" t="n"/>
+      <c r="O14" s="27" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
@@ -6860,6 +6916,8 @@
       </c>
       <c r="L15" s="24" t="n"/>
       <c r="M15" s="24" t="n"/>
+      <c r="N15" s="24" t="n"/>
+      <c r="O15" s="27" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
@@ -6913,6 +6971,8 @@
       </c>
       <c r="L16" s="24" t="n"/>
       <c r="M16" s="24" t="n"/>
+      <c r="N16" s="24" t="n"/>
+      <c r="O16" s="27" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
@@ -6966,6 +7026,8 @@
       </c>
       <c r="L17" s="24" t="n"/>
       <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="n"/>
+      <c r="O17" s="27" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
@@ -7013,6 +7075,8 @@
       <c r="K18" s="25" t="n"/>
       <c r="L18" s="24" t="n"/>
       <c r="M18" s="24" t="n"/>
+      <c r="N18" s="24" t="n"/>
+      <c r="O18" s="27" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
@@ -7066,6 +7130,8 @@
       </c>
       <c r="L19" s="24" t="n"/>
       <c r="M19" s="24" t="n"/>
+      <c r="N19" s="24" t="n"/>
+      <c r="O19" s="27" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
@@ -7119,6 +7185,8 @@
       </c>
       <c r="L20" s="24" t="n"/>
       <c r="M20" s="24" t="n"/>
+      <c r="N20" s="24" t="n"/>
+      <c r="O20" s="27" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
@@ -7166,6 +7234,8 @@
       <c r="K21" s="25" t="n"/>
       <c r="L21" s="24" t="n"/>
       <c r="M21" s="24" t="n"/>
+      <c r="N21" s="24" t="n"/>
+      <c r="O21" s="27" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
@@ -7209,6 +7279,8 @@
       <c r="K22" s="25" t="n"/>
       <c r="L22" s="24" t="n"/>
       <c r="M22" s="24" t="n"/>
+      <c r="N22" s="24" t="n"/>
+      <c r="O22" s="27" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
@@ -7252,6 +7324,8 @@
       <c r="K23" s="25" t="n"/>
       <c r="L23" s="24" t="n"/>
       <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="n"/>
+      <c r="O23" s="27" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
@@ -7295,6 +7369,8 @@
       <c r="K24" s="25" t="n"/>
       <c r="L24" s="24" t="n"/>
       <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="n"/>
+      <c r="O24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="24" t="n"/>
@@ -7310,6 +7386,8 @@
       <c r="K25" s="25" t="n"/>
       <c r="L25" s="24" t="n"/>
       <c r="M25" s="24" t="n"/>
+      <c r="N25" s="24" t="n"/>
+      <c r="O25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="n"/>
@@ -7325,6 +7403,8 @@
       <c r="K26" s="25" t="n"/>
       <c r="L26" s="24" t="n"/>
       <c r="M26" s="24" t="n"/>
+      <c r="N26" s="24" t="n"/>
+      <c r="O26" s="27" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="24" t="n"/>
@@ -7340,6 +7420,8 @@
       <c r="K27" s="25" t="n"/>
       <c r="L27" s="24" t="n"/>
       <c r="M27" s="24" t="n"/>
+      <c r="N27" s="24" t="n"/>
+      <c r="O27" s="27" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="n"/>
@@ -7355,6 +7437,8 @@
       <c r="K28" s="25" t="n"/>
       <c r="L28" s="24" t="n"/>
       <c r="M28" s="24" t="n"/>
+      <c r="N28" s="24" t="n"/>
+      <c r="O28" s="27" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="24" t="n"/>
@@ -7370,6 +7454,8 @@
       <c r="K29" s="25" t="n"/>
       <c r="L29" s="24" t="n"/>
       <c r="M29" s="24" t="n"/>
+      <c r="N29" s="24" t="n"/>
+      <c r="O29" s="27" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="24" t="n"/>
@@ -7385,6 +7471,8 @@
       <c r="K30" s="25" t="n"/>
       <c r="L30" s="24" t="n"/>
       <c r="M30" s="24" t="n"/>
+      <c r="N30" s="24" t="n"/>
+      <c r="O30" s="27" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="24" t="n"/>
@@ -7400,6 +7488,8 @@
       <c r="K31" s="25" t="n"/>
       <c r="L31" s="24" t="n"/>
       <c r="M31" s="24" t="n"/>
+      <c r="N31" s="24" t="n"/>
+      <c r="O31" s="27" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="24" t="n"/>
@@ -7415,6 +7505,8 @@
       <c r="K32" s="25" t="n"/>
       <c r="L32" s="24" t="n"/>
       <c r="M32" s="24" t="n"/>
+      <c r="N32" s="24" t="n"/>
+      <c r="O32" s="27" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="24" t="n"/>
@@ -7430,6 +7522,8 @@
       <c r="K33" s="25" t="n"/>
       <c r="L33" s="24" t="n"/>
       <c r="M33" s="24" t="n"/>
+      <c r="N33" s="24" t="n"/>
+      <c r="O33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="n"/>
@@ -7445,6 +7539,8 @@
       <c r="K34" s="25" t="n"/>
       <c r="L34" s="24" t="n"/>
       <c r="M34" s="24" t="n"/>
+      <c r="N34" s="24" t="n"/>
+      <c r="O34" s="27" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="24" t="n"/>
@@ -7460,6 +7556,8 @@
       <c r="K35" s="25" t="n"/>
       <c r="L35" s="24" t="n"/>
       <c r="M35" s="24" t="n"/>
+      <c r="N35" s="24" t="n"/>
+      <c r="O35" s="27" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="24" t="n"/>
@@ -7475,6 +7573,8 @@
       <c r="K36" s="25" t="n"/>
       <c r="L36" s="24" t="n"/>
       <c r="M36" s="24" t="n"/>
+      <c r="N36" s="24" t="n"/>
+      <c r="O36" s="27" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="24" t="n"/>
@@ -7490,6 +7590,8 @@
       <c r="K37" s="25" t="n"/>
       <c r="L37" s="24" t="n"/>
       <c r="M37" s="24" t="n"/>
+      <c r="N37" s="24" t="n"/>
+      <c r="O37" s="27" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="24" t="n"/>
@@ -7505,6 +7607,8 @@
       <c r="K38" s="25" t="n"/>
       <c r="L38" s="24" t="n"/>
       <c r="M38" s="24" t="n"/>
+      <c r="N38" s="24" t="n"/>
+      <c r="O38" s="27" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="24" t="n"/>
@@ -7520,6 +7624,8 @@
       <c r="K39" s="25" t="n"/>
       <c r="L39" s="24" t="n"/>
       <c r="M39" s="24" t="n"/>
+      <c r="N39" s="24" t="n"/>
+      <c r="O39" s="27" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="24" t="n"/>
@@ -7535,6 +7641,8 @@
       <c r="K40" s="25" t="n"/>
       <c r="L40" s="24" t="n"/>
       <c r="M40" s="24" t="n"/>
+      <c r="N40" s="24" t="n"/>
+      <c r="O40" s="27" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="24" t="n"/>
@@ -7550,6 +7658,8 @@
       <c r="K41" s="25" t="n"/>
       <c r="L41" s="24" t="n"/>
       <c r="M41" s="24" t="n"/>
+      <c r="N41" s="24" t="n"/>
+      <c r="O41" s="27" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="24" t="n"/>
@@ -7565,6 +7675,8 @@
       <c r="K42" s="25" t="n"/>
       <c r="L42" s="24" t="n"/>
       <c r="M42" s="24" t="n"/>
+      <c r="N42" s="24" t="n"/>
+      <c r="O42" s="27" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="24" t="n"/>
@@ -7580,6 +7692,8 @@
       <c r="K43" s="25" t="n"/>
       <c r="L43" s="24" t="n"/>
       <c r="M43" s="24" t="n"/>
+      <c r="N43" s="24" t="n"/>
+      <c r="O43" s="27" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="24" t="n"/>
@@ -7595,6 +7709,8 @@
       <c r="K44" s="25" t="n"/>
       <c r="L44" s="24" t="n"/>
       <c r="M44" s="24" t="n"/>
+      <c r="N44" s="24" t="n"/>
+      <c r="O44" s="27" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="24" t="n"/>
@@ -7610,6 +7726,8 @@
       <c r="K45" s="25" t="n"/>
       <c r="L45" s="24" t="n"/>
       <c r="M45" s="24" t="n"/>
+      <c r="N45" s="24" t="n"/>
+      <c r="O45" s="27" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="24" t="n"/>
@@ -7625,6 +7743,8 @@
       <c r="K46" s="25" t="n"/>
       <c r="L46" s="24" t="n"/>
       <c r="M46" s="24" t="n"/>
+      <c r="N46" s="24" t="n"/>
+      <c r="O46" s="27" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="24" t="n"/>
@@ -7640,6 +7760,8 @@
       <c r="K47" s="25" t="n"/>
       <c r="L47" s="24" t="n"/>
       <c r="M47" s="24" t="n"/>
+      <c r="N47" s="24" t="n"/>
+      <c r="O47" s="27" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="24" t="n"/>
@@ -7655,6 +7777,8 @@
       <c r="K48" s="25" t="n"/>
       <c r="L48" s="24" t="n"/>
       <c r="M48" s="24" t="n"/>
+      <c r="N48" s="24" t="n"/>
+      <c r="O48" s="27" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="24" t="n"/>
@@ -7670,6 +7794,8 @@
       <c r="K49" s="25" t="n"/>
       <c r="L49" s="24" t="n"/>
       <c r="M49" s="24" t="n"/>
+      <c r="N49" s="24" t="n"/>
+      <c r="O49" s="27" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="24" t="n"/>
@@ -7685,6 +7811,8 @@
       <c r="K50" s="25" t="n"/>
       <c r="L50" s="24" t="n"/>
       <c r="M50" s="24" t="n"/>
+      <c r="N50" s="24" t="n"/>
+      <c r="O50" s="27" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="24" t="n"/>
@@ -7700,6 +7828,8 @@
       <c r="K51" s="25" t="n"/>
       <c r="L51" s="24" t="n"/>
       <c r="M51" s="24" t="n"/>
+      <c r="N51" s="24" t="n"/>
+      <c r="O51" s="27" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="24" t="n"/>
@@ -7715,6 +7845,8 @@
       <c r="K52" s="25" t="n"/>
       <c r="L52" s="24" t="n"/>
       <c r="M52" s="24" t="n"/>
+      <c r="N52" s="24" t="n"/>
+      <c r="O52" s="27" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="24" t="n"/>
@@ -7730,6 +7862,8 @@
       <c r="K53" s="25" t="n"/>
       <c r="L53" s="24" t="n"/>
       <c r="M53" s="24" t="n"/>
+      <c r="N53" s="24" t="n"/>
+      <c r="O53" s="27" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="24" t="n"/>
@@ -7745,6 +7879,8 @@
       <c r="K54" s="25" t="n"/>
       <c r="L54" s="24" t="n"/>
       <c r="M54" s="24" t="n"/>
+      <c r="N54" s="24" t="n"/>
+      <c r="O54" s="27" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="24" t="n"/>
@@ -7760,6 +7896,8 @@
       <c r="K55" s="25" t="n"/>
       <c r="L55" s="24" t="n"/>
       <c r="M55" s="24" t="n"/>
+      <c r="N55" s="24" t="n"/>
+      <c r="O55" s="27" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="24" t="n"/>
@@ -7775,6 +7913,8 @@
       <c r="K56" s="25" t="n"/>
       <c r="L56" s="24" t="n"/>
       <c r="M56" s="24" t="n"/>
+      <c r="N56" s="24" t="n"/>
+      <c r="O56" s="27" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="24" t="n"/>
@@ -7790,6 +7930,8 @@
       <c r="K57" s="25" t="n"/>
       <c r="L57" s="24" t="n"/>
       <c r="M57" s="24" t="n"/>
+      <c r="N57" s="24" t="n"/>
+      <c r="O57" s="27" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="24" t="n"/>
@@ -7805,6 +7947,8 @@
       <c r="K58" s="25" t="n"/>
       <c r="L58" s="24" t="n"/>
       <c r="M58" s="24" t="n"/>
+      <c r="N58" s="24" t="n"/>
+      <c r="O58" s="27" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="24" t="n"/>
@@ -7820,6 +7964,8 @@
       <c r="K59" s="25" t="n"/>
       <c r="L59" s="24" t="n"/>
       <c r="M59" s="24" t="n"/>
+      <c r="N59" s="24" t="n"/>
+      <c r="O59" s="27" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="24" t="n"/>
@@ -7835,6 +7981,8 @@
       <c r="K60" s="25" t="n"/>
       <c r="L60" s="24" t="n"/>
       <c r="M60" s="24" t="n"/>
+      <c r="N60" s="24" t="n"/>
+      <c r="O60" s="27" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="24" t="n"/>
@@ -7850,6 +7998,8 @@
       <c r="K61" s="25" t="n"/>
       <c r="L61" s="24" t="n"/>
       <c r="M61" s="24" t="n"/>
+      <c r="N61" s="24" t="n"/>
+      <c r="O61" s="27" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="24" t="n"/>
@@ -7865,6 +8015,8 @@
       <c r="K62" s="25" t="n"/>
       <c r="L62" s="24" t="n"/>
       <c r="M62" s="24" t="n"/>
+      <c r="N62" s="24" t="n"/>
+      <c r="O62" s="27" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="24" t="n"/>
@@ -7880,6 +8032,8 @@
       <c r="K63" s="25" t="n"/>
       <c r="L63" s="24" t="n"/>
       <c r="M63" s="24" t="n"/>
+      <c r="N63" s="24" t="n"/>
+      <c r="O63" s="27" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="24" t="n"/>
@@ -7895,6 +8049,8 @@
       <c r="K64" s="25" t="n"/>
       <c r="L64" s="24" t="n"/>
       <c r="M64" s="24" t="n"/>
+      <c r="N64" s="24" t="n"/>
+      <c r="O64" s="27" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="24" t="n"/>
@@ -7910,6 +8066,8 @@
       <c r="K65" s="25" t="n"/>
       <c r="L65" s="24" t="n"/>
       <c r="M65" s="24" t="n"/>
+      <c r="N65" s="24" t="n"/>
+      <c r="O65" s="27" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="24" t="n"/>
@@ -7925,6 +8083,8 @@
       <c r="K66" s="25" t="n"/>
       <c r="L66" s="24" t="n"/>
       <c r="M66" s="24" t="n"/>
+      <c r="N66" s="24" t="n"/>
+      <c r="O66" s="27" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="24" t="n"/>
@@ -7940,6 +8100,8 @@
       <c r="K67" s="25" t="n"/>
       <c r="L67" s="24" t="n"/>
       <c r="M67" s="24" t="n"/>
+      <c r="N67" s="24" t="n"/>
+      <c r="O67" s="27" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="24" t="n"/>
@@ -7955,6 +8117,8 @@
       <c r="K68" s="25" t="n"/>
       <c r="L68" s="24" t="n"/>
       <c r="M68" s="24" t="n"/>
+      <c r="N68" s="24" t="n"/>
+      <c r="O68" s="27" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="24" t="n"/>
@@ -7970,6 +8134,8 @@
       <c r="K69" s="25" t="n"/>
       <c r="L69" s="24" t="n"/>
       <c r="M69" s="24" t="n"/>
+      <c r="N69" s="24" t="n"/>
+      <c r="O69" s="27" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="24" t="n"/>
@@ -7985,6 +8151,8 @@
       <c r="K70" s="25" t="n"/>
       <c r="L70" s="24" t="n"/>
       <c r="M70" s="24" t="n"/>
+      <c r="N70" s="24" t="n"/>
+      <c r="O70" s="27" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="24" t="n"/>
@@ -8000,6 +8168,8 @@
       <c r="K71" s="25" t="n"/>
       <c r="L71" s="24" t="n"/>
       <c r="M71" s="24" t="n"/>
+      <c r="N71" s="24" t="n"/>
+      <c r="O71" s="27" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="24" t="n"/>
@@ -8015,6 +8185,8 @@
       <c r="K72" s="25" t="n"/>
       <c r="L72" s="24" t="n"/>
       <c r="M72" s="24" t="n"/>
+      <c r="N72" s="24" t="n"/>
+      <c r="O72" s="27" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="24" t="n"/>
@@ -8030,6 +8202,8 @@
       <c r="K73" s="25" t="n"/>
       <c r="L73" s="24" t="n"/>
       <c r="M73" s="24" t="n"/>
+      <c r="N73" s="24" t="n"/>
+      <c r="O73" s="27" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="24" t="n"/>
@@ -8045,6 +8219,8 @@
       <c r="K74" s="25" t="n"/>
       <c r="L74" s="24" t="n"/>
       <c r="M74" s="24" t="n"/>
+      <c r="N74" s="24" t="n"/>
+      <c r="O74" s="27" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="24" t="n"/>
@@ -8060,6 +8236,8 @@
       <c r="K75" s="25" t="n"/>
       <c r="L75" s="24" t="n"/>
       <c r="M75" s="24" t="n"/>
+      <c r="N75" s="24" t="n"/>
+      <c r="O75" s="27" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="24" t="n"/>
@@ -8075,6 +8253,8 @@
       <c r="K76" s="25" t="n"/>
       <c r="L76" s="24" t="n"/>
       <c r="M76" s="24" t="n"/>
+      <c r="N76" s="24" t="n"/>
+      <c r="O76" s="27" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="24" t="n"/>
@@ -8090,6 +8270,8 @@
       <c r="K77" s="25" t="n"/>
       <c r="L77" s="24" t="n"/>
       <c r="M77" s="24" t="n"/>
+      <c r="N77" s="24" t="n"/>
+      <c r="O77" s="27" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="24" t="n"/>
@@ -8105,6 +8287,8 @@
       <c r="K78" s="25" t="n"/>
       <c r="L78" s="24" t="n"/>
       <c r="M78" s="24" t="n"/>
+      <c r="N78" s="24" t="n"/>
+      <c r="O78" s="27" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="24" t="n"/>
@@ -8120,6 +8304,8 @@
       <c r="K79" s="25" t="n"/>
       <c r="L79" s="24" t="n"/>
       <c r="M79" s="24" t="n"/>
+      <c r="N79" s="24" t="n"/>
+      <c r="O79" s="27" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="24" t="n"/>
@@ -8135,6 +8321,8 @@
       <c r="K80" s="25" t="n"/>
       <c r="L80" s="24" t="n"/>
       <c r="M80" s="24" t="n"/>
+      <c r="N80" s="24" t="n"/>
+      <c r="O80" s="27" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="24" t="n"/>
@@ -8150,6 +8338,8 @@
       <c r="K81" s="25" t="n"/>
       <c r="L81" s="24" t="n"/>
       <c r="M81" s="24" t="n"/>
+      <c r="N81" s="24" t="n"/>
+      <c r="O81" s="27" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="24" t="n"/>
@@ -8165,6 +8355,8 @@
       <c r="K82" s="25" t="n"/>
       <c r="L82" s="24" t="n"/>
       <c r="M82" s="24" t="n"/>
+      <c r="N82" s="24" t="n"/>
+      <c r="O82" s="27" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="24" t="n"/>
@@ -8180,6 +8372,8 @@
       <c r="K83" s="25" t="n"/>
       <c r="L83" s="24" t="n"/>
       <c r="M83" s="24" t="n"/>
+      <c r="N83" s="24" t="n"/>
+      <c r="O83" s="27" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="24" t="n"/>
@@ -8195,6 +8389,8 @@
       <c r="K84" s="25" t="n"/>
       <c r="L84" s="24" t="n"/>
       <c r="M84" s="24" t="n"/>
+      <c r="N84" s="24" t="n"/>
+      <c r="O84" s="27" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="24" t="n"/>
@@ -8210,6 +8406,8 @@
       <c r="K85" s="25" t="n"/>
       <c r="L85" s="24" t="n"/>
       <c r="M85" s="24" t="n"/>
+      <c r="N85" s="24" t="n"/>
+      <c r="O85" s="27" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="24" t="n"/>
@@ -8225,6 +8423,8 @@
       <c r="K86" s="25" t="n"/>
       <c r="L86" s="24" t="n"/>
       <c r="M86" s="24" t="n"/>
+      <c r="N86" s="24" t="n"/>
+      <c r="O86" s="27" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="24" t="n"/>
@@ -8240,6 +8440,8 @@
       <c r="K87" s="25" t="n"/>
       <c r="L87" s="24" t="n"/>
       <c r="M87" s="24" t="n"/>
+      <c r="N87" s="24" t="n"/>
+      <c r="O87" s="27" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="24" t="n"/>
@@ -8255,6 +8457,8 @@
       <c r="K88" s="25" t="n"/>
       <c r="L88" s="24" t="n"/>
       <c r="M88" s="24" t="n"/>
+      <c r="N88" s="24" t="n"/>
+      <c r="O88" s="27" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="24" t="n"/>
@@ -8270,6 +8474,8 @@
       <c r="K89" s="25" t="n"/>
       <c r="L89" s="24" t="n"/>
       <c r="M89" s="24" t="n"/>
+      <c r="N89" s="24" t="n"/>
+      <c r="O89" s="27" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="24" t="n"/>
@@ -8285,6 +8491,8 @@
       <c r="K90" s="25" t="n"/>
       <c r="L90" s="24" t="n"/>
       <c r="M90" s="24" t="n"/>
+      <c r="N90" s="24" t="n"/>
+      <c r="O90" s="27" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="24" t="n"/>
@@ -8300,6 +8508,8 @@
       <c r="K91" s="25" t="n"/>
       <c r="L91" s="24" t="n"/>
       <c r="M91" s="24" t="n"/>
+      <c r="N91" s="24" t="n"/>
+      <c r="O91" s="27" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="24" t="n"/>
@@ -8315,6 +8525,8 @@
       <c r="K92" s="25" t="n"/>
       <c r="L92" s="24" t="n"/>
       <c r="M92" s="24" t="n"/>
+      <c r="N92" s="24" t="n"/>
+      <c r="O92" s="27" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="24" t="n"/>
@@ -8330,6 +8542,8 @@
       <c r="K93" s="25" t="n"/>
       <c r="L93" s="24" t="n"/>
       <c r="M93" s="24" t="n"/>
+      <c r="N93" s="24" t="n"/>
+      <c r="O93" s="27" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="24" t="n"/>
@@ -8345,6 +8559,8 @@
       <c r="K94" s="25" t="n"/>
       <c r="L94" s="24" t="n"/>
       <c r="M94" s="24" t="n"/>
+      <c r="N94" s="24" t="n"/>
+      <c r="O94" s="27" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="24" t="n"/>
@@ -8360,6 +8576,8 @@
       <c r="K95" s="25" t="n"/>
       <c r="L95" s="24" t="n"/>
       <c r="M95" s="24" t="n"/>
+      <c r="N95" s="24" t="n"/>
+      <c r="O95" s="27" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="24" t="n"/>
@@ -8375,6 +8593,8 @@
       <c r="K96" s="25" t="n"/>
       <c r="L96" s="24" t="n"/>
       <c r="M96" s="24" t="n"/>
+      <c r="N96" s="24" t="n"/>
+      <c r="O96" s="27" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="24" t="n"/>
@@ -8390,6 +8610,8 @@
       <c r="K97" s="25" t="n"/>
       <c r="L97" s="24" t="n"/>
       <c r="M97" s="24" t="n"/>
+      <c r="N97" s="24" t="n"/>
+      <c r="O97" s="27" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="24" t="n"/>
@@ -8405,6 +8627,8 @@
       <c r="K98" s="25" t="n"/>
       <c r="L98" s="24" t="n"/>
       <c r="M98" s="24" t="n"/>
+      <c r="N98" s="24" t="n"/>
+      <c r="O98" s="27" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="24" t="n"/>
@@ -8420,6 +8644,8 @@
       <c r="K99" s="25" t="n"/>
       <c r="L99" s="24" t="n"/>
       <c r="M99" s="24" t="n"/>
+      <c r="N99" s="24" t="n"/>
+      <c r="O99" s="27" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="24" t="n"/>
@@ -8435,6 +8661,8 @@
       <c r="K100" s="25" t="n"/>
       <c r="L100" s="24" t="n"/>
       <c r="M100" s="24" t="n"/>
+      <c r="N100" s="24" t="n"/>
+      <c r="O100" s="27" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="24" t="n"/>
@@ -8450,6 +8678,8 @@
       <c r="K101" s="25" t="n"/>
       <c r="L101" s="24" t="n"/>
       <c r="M101" s="24" t="n"/>
+      <c r="N101" s="24" t="n"/>
+      <c r="O101" s="27" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="24" t="n"/>
@@ -8465,6 +8695,8 @@
       <c r="K102" s="25" t="n"/>
       <c r="L102" s="24" t="n"/>
       <c r="M102" s="24" t="n"/>
+      <c r="N102" s="24" t="n"/>
+      <c r="O102" s="27" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="24" t="n"/>
@@ -8480,6 +8712,8 @@
       <c r="K103" s="25" t="n"/>
       <c r="L103" s="24" t="n"/>
       <c r="M103" s="24" t="n"/>
+      <c r="N103" s="24" t="n"/>
+      <c r="O103" s="27" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="24" t="n"/>
@@ -8495,6 +8729,8 @@
       <c r="K104" s="25" t="n"/>
       <c r="L104" s="24" t="n"/>
       <c r="M104" s="24" t="n"/>
+      <c r="N104" s="24" t="n"/>
+      <c r="O104" s="27" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="24" t="n"/>
@@ -8510,6 +8746,8 @@
       <c r="K105" s="25" t="n"/>
       <c r="L105" s="24" t="n"/>
       <c r="M105" s="24" t="n"/>
+      <c r="N105" s="24" t="n"/>
+      <c r="O105" s="27" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="24" t="n"/>
@@ -8525,6 +8763,8 @@
       <c r="K106" s="25" t="n"/>
       <c r="L106" s="24" t="n"/>
       <c r="M106" s="24" t="n"/>
+      <c r="N106" s="24" t="n"/>
+      <c r="O106" s="27" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="24" t="n"/>
@@ -8540,6 +8780,8 @@
       <c r="K107" s="25" t="n"/>
       <c r="L107" s="24" t="n"/>
       <c r="M107" s="24" t="n"/>
+      <c r="N107" s="24" t="n"/>
+      <c r="O107" s="27" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="24" t="n"/>
@@ -8555,6 +8797,8 @@
       <c r="K108" s="25" t="n"/>
       <c r="L108" s="24" t="n"/>
       <c r="M108" s="24" t="n"/>
+      <c r="N108" s="24" t="n"/>
+      <c r="O108" s="27" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="24" t="n"/>
@@ -8570,6 +8814,8 @@
       <c r="K109" s="25" t="n"/>
       <c r="L109" s="24" t="n"/>
       <c r="M109" s="24" t="n"/>
+      <c r="N109" s="24" t="n"/>
+      <c r="O109" s="27" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="24" t="n"/>
@@ -8585,6 +8831,8 @@
       <c r="K110" s="25" t="n"/>
       <c r="L110" s="24" t="n"/>
       <c r="M110" s="24" t="n"/>
+      <c r="N110" s="24" t="n"/>
+      <c r="O110" s="27" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="24" t="n"/>
@@ -8600,6 +8848,8 @@
       <c r="K111" s="25" t="n"/>
       <c r="L111" s="24" t="n"/>
       <c r="M111" s="24" t="n"/>
+      <c r="N111" s="24" t="n"/>
+      <c r="O111" s="27" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="24" t="n"/>
@@ -8615,6 +8865,8 @@
       <c r="K112" s="25" t="n"/>
       <c r="L112" s="24" t="n"/>
       <c r="M112" s="24" t="n"/>
+      <c r="N112" s="24" t="n"/>
+      <c r="O112" s="27" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="24" t="n"/>
@@ -8630,6 +8882,8 @@
       <c r="K113" s="25" t="n"/>
       <c r="L113" s="24" t="n"/>
       <c r="M113" s="24" t="n"/>
+      <c r="N113" s="24" t="n"/>
+      <c r="O113" s="27" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="24" t="n"/>
@@ -8645,6 +8899,8 @@
       <c r="K114" s="25" t="n"/>
       <c r="L114" s="24" t="n"/>
       <c r="M114" s="24" t="n"/>
+      <c r="N114" s="24" t="n"/>
+      <c r="O114" s="27" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="24" t="n"/>
@@ -8660,6 +8916,8 @@
       <c r="K115" s="25" t="n"/>
       <c r="L115" s="24" t="n"/>
       <c r="M115" s="24" t="n"/>
+      <c r="N115" s="24" t="n"/>
+      <c r="O115" s="27" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="24" t="n"/>
@@ -8675,6 +8933,8 @@
       <c r="K116" s="25" t="n"/>
       <c r="L116" s="24" t="n"/>
       <c r="M116" s="24" t="n"/>
+      <c r="N116" s="24" t="n"/>
+      <c r="O116" s="27" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="24" t="n"/>
@@ -8690,6 +8950,8 @@
       <c r="K117" s="25" t="n"/>
       <c r="L117" s="24" t="n"/>
       <c r="M117" s="24" t="n"/>
+      <c r="N117" s="24" t="n"/>
+      <c r="O117" s="27" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="24" t="n"/>
@@ -8705,6 +8967,8 @@
       <c r="K118" s="25" t="n"/>
       <c r="L118" s="24" t="n"/>
       <c r="M118" s="24" t="n"/>
+      <c r="N118" s="24" t="n"/>
+      <c r="O118" s="27" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="24" t="n"/>
@@ -8720,6 +8984,8 @@
       <c r="K119" s="25" t="n"/>
       <c r="L119" s="24" t="n"/>
       <c r="M119" s="24" t="n"/>
+      <c r="N119" s="24" t="n"/>
+      <c r="O119" s="27" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="24" t="n"/>
@@ -8735,6 +9001,8 @@
       <c r="K120" s="25" t="n"/>
       <c r="L120" s="24" t="n"/>
       <c r="M120" s="24" t="n"/>
+      <c r="N120" s="24" t="n"/>
+      <c r="O120" s="27" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="24" t="n"/>
@@ -8750,6 +9018,8 @@
       <c r="K121" s="25" t="n"/>
       <c r="L121" s="24" t="n"/>
       <c r="M121" s="24" t="n"/>
+      <c r="N121" s="24" t="n"/>
+      <c r="O121" s="27" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="24" t="n"/>
@@ -8765,6 +9035,8 @@
       <c r="K122" s="25" t="n"/>
       <c r="L122" s="24" t="n"/>
       <c r="M122" s="24" t="n"/>
+      <c r="N122" s="24" t="n"/>
+      <c r="O122" s="27" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="24" t="n"/>
@@ -8780,6 +9052,8 @@
       <c r="K123" s="25" t="n"/>
       <c r="L123" s="24" t="n"/>
       <c r="M123" s="24" t="n"/>
+      <c r="N123" s="24" t="n"/>
+      <c r="O123" s="27" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="24" t="n"/>
@@ -8795,6 +9069,8 @@
       <c r="K124" s="25" t="n"/>
       <c r="L124" s="24" t="n"/>
       <c r="M124" s="24" t="n"/>
+      <c r="N124" s="24" t="n"/>
+      <c r="O124" s="27" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="24" t="n"/>
@@ -8810,6 +9086,8 @@
       <c r="K125" s="25" t="n"/>
       <c r="L125" s="24" t="n"/>
       <c r="M125" s="24" t="n"/>
+      <c r="N125" s="24" t="n"/>
+      <c r="O125" s="27" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="24" t="n"/>
@@ -8825,6 +9103,8 @@
       <c r="K126" s="25" t="n"/>
       <c r="L126" s="24" t="n"/>
       <c r="M126" s="24" t="n"/>
+      <c r="N126" s="24" t="n"/>
+      <c r="O126" s="27" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="24" t="n"/>
@@ -8840,6 +9120,8 @@
       <c r="K127" s="25" t="n"/>
       <c r="L127" s="24" t="n"/>
       <c r="M127" s="24" t="n"/>
+      <c r="N127" s="24" t="n"/>
+      <c r="O127" s="27" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="24" t="n"/>
@@ -8855,6 +9137,8 @@
       <c r="K128" s="25" t="n"/>
       <c r="L128" s="24" t="n"/>
       <c r="M128" s="24" t="n"/>
+      <c r="N128" s="24" t="n"/>
+      <c r="O128" s="27" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="24" t="n"/>
@@ -8870,6 +9154,8 @@
       <c r="K129" s="25" t="n"/>
       <c r="L129" s="24" t="n"/>
       <c r="M129" s="24" t="n"/>
+      <c r="N129" s="24" t="n"/>
+      <c r="O129" s="27" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="24" t="n"/>
@@ -8885,6 +9171,8 @@
       <c r="K130" s="25" t="n"/>
       <c r="L130" s="24" t="n"/>
       <c r="M130" s="24" t="n"/>
+      <c r="N130" s="24" t="n"/>
+      <c r="O130" s="27" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="24" t="n"/>
@@ -8900,6 +9188,8 @@
       <c r="K131" s="25" t="n"/>
       <c r="L131" s="24" t="n"/>
       <c r="M131" s="24" t="n"/>
+      <c r="N131" s="24" t="n"/>
+      <c r="O131" s="27" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="24" t="n"/>
@@ -8915,6 +9205,8 @@
       <c r="K132" s="25" t="n"/>
       <c r="L132" s="24" t="n"/>
       <c r="M132" s="24" t="n"/>
+      <c r="N132" s="24" t="n"/>
+      <c r="O132" s="27" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="24" t="n"/>
@@ -8930,6 +9222,8 @@
       <c r="K133" s="25" t="n"/>
       <c r="L133" s="24" t="n"/>
       <c r="M133" s="24" t="n"/>
+      <c r="N133" s="24" t="n"/>
+      <c r="O133" s="27" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="24" t="n"/>
@@ -8945,6 +9239,8 @@
       <c r="K134" s="25" t="n"/>
       <c r="L134" s="24" t="n"/>
       <c r="M134" s="24" t="n"/>
+      <c r="N134" s="24" t="n"/>
+      <c r="O134" s="27" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="24" t="n"/>
@@ -8960,6 +9256,8 @@
       <c r="K135" s="25" t="n"/>
       <c r="L135" s="24" t="n"/>
       <c r="M135" s="24" t="n"/>
+      <c r="N135" s="24" t="n"/>
+      <c r="O135" s="27" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="24" t="n"/>
@@ -8975,6 +9273,8 @@
       <c r="K136" s="25" t="n"/>
       <c r="L136" s="24" t="n"/>
       <c r="M136" s="24" t="n"/>
+      <c r="N136" s="24" t="n"/>
+      <c r="O136" s="27" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="24" t="n"/>
@@ -8990,6 +9290,8 @@
       <c r="K137" s="25" t="n"/>
       <c r="L137" s="24" t="n"/>
       <c r="M137" s="24" t="n"/>
+      <c r="N137" s="24" t="n"/>
+      <c r="O137" s="27" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="24" t="n"/>
@@ -9005,6 +9307,8 @@
       <c r="K138" s="25" t="n"/>
       <c r="L138" s="24" t="n"/>
       <c r="M138" s="24" t="n"/>
+      <c r="N138" s="24" t="n"/>
+      <c r="O138" s="27" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="24" t="n"/>
@@ -9020,6 +9324,8 @@
       <c r="K139" s="25" t="n"/>
       <c r="L139" s="24" t="n"/>
       <c r="M139" s="24" t="n"/>
+      <c r="N139" s="24" t="n"/>
+      <c r="O139" s="27" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="24" t="n"/>
@@ -9035,6 +9341,8 @@
       <c r="K140" s="25" t="n"/>
       <c r="L140" s="24" t="n"/>
       <c r="M140" s="24" t="n"/>
+      <c r="N140" s="24" t="n"/>
+      <c r="O140" s="27" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="24" t="n"/>
@@ -9050,6 +9358,8 @@
       <c r="K141" s="25" t="n"/>
       <c r="L141" s="24" t="n"/>
       <c r="M141" s="24" t="n"/>
+      <c r="N141" s="24" t="n"/>
+      <c r="O141" s="27" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="24" t="n"/>
@@ -9065,6 +9375,8 @@
       <c r="K142" s="25" t="n"/>
       <c r="L142" s="24" t="n"/>
       <c r="M142" s="24" t="n"/>
+      <c r="N142" s="24" t="n"/>
+      <c r="O142" s="27" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="24" t="n"/>
@@ -9080,6 +9392,8 @@
       <c r="K143" s="25" t="n"/>
       <c r="L143" s="24" t="n"/>
       <c r="M143" s="24" t="n"/>
+      <c r="N143" s="24" t="n"/>
+      <c r="O143" s="27" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="24" t="n"/>
@@ -9095,6 +9409,8 @@
       <c r="K144" s="25" t="n"/>
       <c r="L144" s="24" t="n"/>
       <c r="M144" s="24" t="n"/>
+      <c r="N144" s="24" t="n"/>
+      <c r="O144" s="27" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="24" t="n"/>
@@ -9110,6 +9426,8 @@
       <c r="K145" s="25" t="n"/>
       <c r="L145" s="24" t="n"/>
       <c r="M145" s="24" t="n"/>
+      <c r="N145" s="24" t="n"/>
+      <c r="O145" s="27" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="24" t="n"/>
@@ -9125,6 +9443,8 @@
       <c r="K146" s="25" t="n"/>
       <c r="L146" s="24" t="n"/>
       <c r="M146" s="24" t="n"/>
+      <c r="N146" s="24" t="n"/>
+      <c r="O146" s="27" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="24" t="n"/>
@@ -9140,6 +9460,8 @@
       <c r="K147" s="25" t="n"/>
       <c r="L147" s="24" t="n"/>
       <c r="M147" s="24" t="n"/>
+      <c r="N147" s="24" t="n"/>
+      <c r="O147" s="27" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="24" t="n"/>
@@ -9155,6 +9477,8 @@
       <c r="K148" s="25" t="n"/>
       <c r="L148" s="24" t="n"/>
       <c r="M148" s="24" t="n"/>
+      <c r="N148" s="24" t="n"/>
+      <c r="O148" s="27" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="24" t="n"/>
@@ -9170,6 +9494,8 @@
       <c r="K149" s="25" t="n"/>
       <c r="L149" s="24" t="n"/>
       <c r="M149" s="24" t="n"/>
+      <c r="N149" s="24" t="n"/>
+      <c r="O149" s="27" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="24" t="n"/>
@@ -9185,6 +9511,8 @@
       <c r="K150" s="25" t="n"/>
       <c r="L150" s="24" t="n"/>
       <c r="M150" s="24" t="n"/>
+      <c r="N150" s="24" t="n"/>
+      <c r="O150" s="27" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="24" t="n"/>
@@ -9200,6 +9528,8 @@
       <c r="K151" s="25" t="n"/>
       <c r="L151" s="24" t="n"/>
       <c r="M151" s="24" t="n"/>
+      <c r="N151" s="24" t="n"/>
+      <c r="O151" s="27" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="24" t="n"/>
@@ -9215,6 +9545,8 @@
       <c r="K152" s="25" t="n"/>
       <c r="L152" s="24" t="n"/>
       <c r="M152" s="24" t="n"/>
+      <c r="N152" s="24" t="n"/>
+      <c r="O152" s="27" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="24" t="n"/>
@@ -9230,6 +9562,8 @@
       <c r="K153" s="25" t="n"/>
       <c r="L153" s="24" t="n"/>
       <c r="M153" s="24" t="n"/>
+      <c r="N153" s="24" t="n"/>
+      <c r="O153" s="27" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="24" t="n"/>
@@ -9245,6 +9579,8 @@
       <c r="K154" s="25" t="n"/>
       <c r="L154" s="24" t="n"/>
       <c r="M154" s="24" t="n"/>
+      <c r="N154" s="24" t="n"/>
+      <c r="O154" s="27" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="24" t="n"/>
@@ -9260,6 +9596,8 @@
       <c r="K155" s="25" t="n"/>
       <c r="L155" s="24" t="n"/>
       <c r="M155" s="24" t="n"/>
+      <c r="N155" s="24" t="n"/>
+      <c r="O155" s="27" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="24" t="n"/>
@@ -9275,6 +9613,8 @@
       <c r="K156" s="25" t="n"/>
       <c r="L156" s="24" t="n"/>
       <c r="M156" s="24" t="n"/>
+      <c r="N156" s="24" t="n"/>
+      <c r="O156" s="27" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="24" t="n"/>
@@ -9290,6 +9630,8 @@
       <c r="K157" s="25" t="n"/>
       <c r="L157" s="24" t="n"/>
       <c r="M157" s="24" t="n"/>
+      <c r="N157" s="24" t="n"/>
+      <c r="O157" s="27" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="24" t="n"/>
@@ -9305,6 +9647,8 @@
       <c r="K158" s="25" t="n"/>
       <c r="L158" s="24" t="n"/>
       <c r="M158" s="24" t="n"/>
+      <c r="N158" s="24" t="n"/>
+      <c r="O158" s="27" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="24" t="n"/>
@@ -9320,6 +9664,8 @@
       <c r="K159" s="25" t="n"/>
       <c r="L159" s="24" t="n"/>
       <c r="M159" s="24" t="n"/>
+      <c r="N159" s="24" t="n"/>
+      <c r="O159" s="27" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="24" t="n"/>
@@ -9335,6 +9681,8 @@
       <c r="K160" s="25" t="n"/>
       <c r="L160" s="24" t="n"/>
       <c r="M160" s="24" t="n"/>
+      <c r="N160" s="24" t="n"/>
+      <c r="O160" s="27" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="24" t="n"/>
@@ -9350,6 +9698,8 @@
       <c r="K161" s="25" t="n"/>
       <c r="L161" s="24" t="n"/>
       <c r="M161" s="24" t="n"/>
+      <c r="N161" s="24" t="n"/>
+      <c r="O161" s="27" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="24" t="n"/>
@@ -9365,6 +9715,8 @@
       <c r="K162" s="25" t="n"/>
       <c r="L162" s="24" t="n"/>
       <c r="M162" s="24" t="n"/>
+      <c r="N162" s="24" t="n"/>
+      <c r="O162" s="27" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="24" t="n"/>
@@ -9380,6 +9732,8 @@
       <c r="K163" s="25" t="n"/>
       <c r="L163" s="24" t="n"/>
       <c r="M163" s="24" t="n"/>
+      <c r="N163" s="24" t="n"/>
+      <c r="O163" s="27" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="24" t="n"/>
@@ -9395,6 +9749,8 @@
       <c r="K164" s="25" t="n"/>
       <c r="L164" s="24" t="n"/>
       <c r="M164" s="24" t="n"/>
+      <c r="N164" s="24" t="n"/>
+      <c r="O164" s="27" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="24" t="n"/>
@@ -9410,6 +9766,8 @@
       <c r="K165" s="25" t="n"/>
       <c r="L165" s="24" t="n"/>
       <c r="M165" s="24" t="n"/>
+      <c r="N165" s="24" t="n"/>
+      <c r="O165" s="27" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="24" t="n"/>
@@ -9425,6 +9783,8 @@
       <c r="K166" s="25" t="n"/>
       <c r="L166" s="24" t="n"/>
       <c r="M166" s="24" t="n"/>
+      <c r="N166" s="24" t="n"/>
+      <c r="O166" s="27" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="24" t="n"/>
@@ -9440,6 +9800,8 @@
       <c r="K167" s="25" t="n"/>
       <c r="L167" s="24" t="n"/>
       <c r="M167" s="24" t="n"/>
+      <c r="N167" s="24" t="n"/>
+      <c r="O167" s="27" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="24" t="n"/>
@@ -9455,6 +9817,8 @@
       <c r="K168" s="25" t="n"/>
       <c r="L168" s="24" t="n"/>
       <c r="M168" s="24" t="n"/>
+      <c r="N168" s="24" t="n"/>
+      <c r="O168" s="27" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="24" t="n"/>
@@ -9470,6 +9834,8 @@
       <c r="K169" s="25" t="n"/>
       <c r="L169" s="24" t="n"/>
       <c r="M169" s="24" t="n"/>
+      <c r="N169" s="24" t="n"/>
+      <c r="O169" s="27" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="24" t="n"/>
@@ -9485,6 +9851,8 @@
       <c r="K170" s="25" t="n"/>
       <c r="L170" s="24" t="n"/>
       <c r="M170" s="24" t="n"/>
+      <c r="N170" s="24" t="n"/>
+      <c r="O170" s="27" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="24" t="n"/>
@@ -9500,6 +9868,8 @@
       <c r="K171" s="25" t="n"/>
       <c r="L171" s="24" t="n"/>
       <c r="M171" s="24" t="n"/>
+      <c r="N171" s="24" t="n"/>
+      <c r="O171" s="27" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="24" t="n"/>
@@ -9515,6 +9885,8 @@
       <c r="K172" s="25" t="n"/>
       <c r="L172" s="24" t="n"/>
       <c r="M172" s="24" t="n"/>
+      <c r="N172" s="24" t="n"/>
+      <c r="O172" s="27" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="24" t="n"/>
@@ -9530,6 +9902,8 @@
       <c r="K173" s="25" t="n"/>
       <c r="L173" s="24" t="n"/>
       <c r="M173" s="24" t="n"/>
+      <c r="N173" s="24" t="n"/>
+      <c r="O173" s="27" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="24" t="n"/>
@@ -9545,6 +9919,8 @@
       <c r="K174" s="25" t="n"/>
       <c r="L174" s="24" t="n"/>
       <c r="M174" s="24" t="n"/>
+      <c r="N174" s="24" t="n"/>
+      <c r="O174" s="27" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="24" t="n"/>
@@ -9560,6 +9936,8 @@
       <c r="K175" s="25" t="n"/>
       <c r="L175" s="24" t="n"/>
       <c r="M175" s="24" t="n"/>
+      <c r="N175" s="24" t="n"/>
+      <c r="O175" s="27" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="24" t="n"/>
@@ -9575,6 +9953,8 @@
       <c r="K176" s="25" t="n"/>
       <c r="L176" s="24" t="n"/>
       <c r="M176" s="24" t="n"/>
+      <c r="N176" s="24" t="n"/>
+      <c r="O176" s="27" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="24" t="n"/>
@@ -9590,6 +9970,8 @@
       <c r="K177" s="25" t="n"/>
       <c r="L177" s="24" t="n"/>
       <c r="M177" s="24" t="n"/>
+      <c r="N177" s="24" t="n"/>
+      <c r="O177" s="27" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="24" t="n"/>
@@ -9605,6 +9987,8 @@
       <c r="K178" s="25" t="n"/>
       <c r="L178" s="24" t="n"/>
       <c r="M178" s="24" t="n"/>
+      <c r="N178" s="24" t="n"/>
+      <c r="O178" s="27" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="24" t="n"/>
@@ -9620,6 +10004,8 @@
       <c r="K179" s="25" t="n"/>
       <c r="L179" s="24" t="n"/>
       <c r="M179" s="24" t="n"/>
+      <c r="N179" s="24" t="n"/>
+      <c r="O179" s="27" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="24" t="n"/>
@@ -9635,6 +10021,8 @@
       <c r="K180" s="25" t="n"/>
       <c r="L180" s="24" t="n"/>
       <c r="M180" s="24" t="n"/>
+      <c r="N180" s="24" t="n"/>
+      <c r="O180" s="27" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="24" t="n"/>
@@ -9650,6 +10038,8 @@
       <c r="K181" s="25" t="n"/>
       <c r="L181" s="24" t="n"/>
       <c r="M181" s="24" t="n"/>
+      <c r="N181" s="24" t="n"/>
+      <c r="O181" s="27" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="24" t="n"/>
@@ -9665,6 +10055,8 @@
       <c r="K182" s="25" t="n"/>
       <c r="L182" s="24" t="n"/>
       <c r="M182" s="24" t="n"/>
+      <c r="N182" s="24" t="n"/>
+      <c r="O182" s="27" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="24" t="n"/>
@@ -9680,6 +10072,8 @@
       <c r="K183" s="25" t="n"/>
       <c r="L183" s="24" t="n"/>
       <c r="M183" s="24" t="n"/>
+      <c r="N183" s="24" t="n"/>
+      <c r="O183" s="27" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="24" t="n"/>
@@ -9695,6 +10089,8 @@
       <c r="K184" s="25" t="n"/>
       <c r="L184" s="24" t="n"/>
       <c r="M184" s="24" t="n"/>
+      <c r="N184" s="24" t="n"/>
+      <c r="O184" s="27" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="24" t="n"/>
@@ -9710,6 +10106,8 @@
       <c r="K185" s="25" t="n"/>
       <c r="L185" s="24" t="n"/>
       <c r="M185" s="24" t="n"/>
+      <c r="N185" s="24" t="n"/>
+      <c r="O185" s="27" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="24" t="n"/>
@@ -9725,6 +10123,8 @@
       <c r="K186" s="25" t="n"/>
       <c r="L186" s="24" t="n"/>
       <c r="M186" s="24" t="n"/>
+      <c r="N186" s="24" t="n"/>
+      <c r="O186" s="27" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="24" t="n"/>
@@ -9740,6 +10140,8 @@
       <c r="K187" s="25" t="n"/>
       <c r="L187" s="24" t="n"/>
       <c r="M187" s="24" t="n"/>
+      <c r="N187" s="24" t="n"/>
+      <c r="O187" s="27" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="24" t="n"/>
@@ -9755,6 +10157,8 @@
       <c r="K188" s="25" t="n"/>
       <c r="L188" s="24" t="n"/>
       <c r="M188" s="24" t="n"/>
+      <c r="N188" s="24" t="n"/>
+      <c r="O188" s="27" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="24" t="n"/>
@@ -9770,6 +10174,8 @@
       <c r="K189" s="25" t="n"/>
       <c r="L189" s="24" t="n"/>
       <c r="M189" s="24" t="n"/>
+      <c r="N189" s="24" t="n"/>
+      <c r="O189" s="27" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="24" t="n"/>
@@ -9785,6 +10191,8 @@
       <c r="K190" s="25" t="n"/>
       <c r="L190" s="24" t="n"/>
       <c r="M190" s="24" t="n"/>
+      <c r="N190" s="24" t="n"/>
+      <c r="O190" s="27" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="24" t="n"/>
@@ -9800,6 +10208,8 @@
       <c r="K191" s="25" t="n"/>
       <c r="L191" s="24" t="n"/>
       <c r="M191" s="24" t="n"/>
+      <c r="N191" s="24" t="n"/>
+      <c r="O191" s="27" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="24" t="n"/>
@@ -9815,6 +10225,8 @@
       <c r="K192" s="25" t="n"/>
       <c r="L192" s="24" t="n"/>
       <c r="M192" s="24" t="n"/>
+      <c r="N192" s="24" t="n"/>
+      <c r="O192" s="27" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="24" t="n"/>
@@ -9830,6 +10242,8 @@
       <c r="K193" s="25" t="n"/>
       <c r="L193" s="24" t="n"/>
       <c r="M193" s="24" t="n"/>
+      <c r="N193" s="24" t="n"/>
+      <c r="O193" s="27" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="24" t="n"/>
@@ -9845,6 +10259,8 @@
       <c r="K194" s="25" t="n"/>
       <c r="L194" s="24" t="n"/>
       <c r="M194" s="24" t="n"/>
+      <c r="N194" s="24" t="n"/>
+      <c r="O194" s="27" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="24" t="n"/>
@@ -9860,6 +10276,8 @@
       <c r="K195" s="25" t="n"/>
       <c r="L195" s="24" t="n"/>
       <c r="M195" s="24" t="n"/>
+      <c r="N195" s="24" t="n"/>
+      <c r="O195" s="27" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="24" t="n"/>
@@ -9875,6 +10293,8 @@
       <c r="K196" s="25" t="n"/>
       <c r="L196" s="24" t="n"/>
       <c r="M196" s="24" t="n"/>
+      <c r="N196" s="24" t="n"/>
+      <c r="O196" s="27" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="24" t="n"/>
@@ -9890,6 +10310,8 @@
       <c r="K197" s="25" t="n"/>
       <c r="L197" s="24" t="n"/>
       <c r="M197" s="24" t="n"/>
+      <c r="N197" s="24" t="n"/>
+      <c r="O197" s="27" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="24" t="n"/>
@@ -9905,6 +10327,8 @@
       <c r="K198" s="25" t="n"/>
       <c r="L198" s="24" t="n"/>
       <c r="M198" s="24" t="n"/>
+      <c r="N198" s="24" t="n"/>
+      <c r="O198" s="27" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="24" t="n"/>
@@ -9920,6 +10344,8 @@
       <c r="K199" s="25" t="n"/>
       <c r="L199" s="24" t="n"/>
       <c r="M199" s="24" t="n"/>
+      <c r="N199" s="24" t="n"/>
+      <c r="O199" s="27" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="24" t="n"/>
@@ -9935,6 +10361,8 @@
       <c r="K200" s="25" t="n"/>
       <c r="L200" s="24" t="n"/>
       <c r="M200" s="24" t="n"/>
+      <c r="N200" s="24" t="n"/>
+      <c r="O200" s="27" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="24" t="n"/>
@@ -9950,6 +10378,8 @@
       <c r="K201" s="25" t="n"/>
       <c r="L201" s="24" t="n"/>
       <c r="M201" s="24" t="n"/>
+      <c r="N201" s="24" t="n"/>
+      <c r="O201" s="27" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="24" t="n"/>
@@ -9965,6 +10395,8 @@
       <c r="K202" s="25" t="n"/>
       <c r="L202" s="24" t="n"/>
       <c r="M202" s="24" t="n"/>
+      <c r="N202" s="24" t="n"/>
+      <c r="O202" s="27" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="24" t="n"/>
@@ -9980,6 +10412,8 @@
       <c r="K203" s="25" t="n"/>
       <c r="L203" s="24" t="n"/>
       <c r="M203" s="24" t="n"/>
+      <c r="N203" s="24" t="n"/>
+      <c r="O203" s="27" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="24" t="n"/>
@@ -9995,6 +10429,8 @@
       <c r="K204" s="25" t="n"/>
       <c r="L204" s="24" t="n"/>
       <c r="M204" s="24" t="n"/>
+      <c r="N204" s="24" t="n"/>
+      <c r="O204" s="27" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="24" t="n"/>
@@ -10010,6 +10446,8 @@
       <c r="K205" s="25" t="n"/>
       <c r="L205" s="24" t="n"/>
       <c r="M205" s="24" t="n"/>
+      <c r="N205" s="24" t="n"/>
+      <c r="O205" s="27" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="24" t="n"/>
@@ -10025,6 +10463,8 @@
       <c r="K206" s="25" t="n"/>
       <c r="L206" s="24" t="n"/>
       <c r="M206" s="24" t="n"/>
+      <c r="N206" s="24" t="n"/>
+      <c r="O206" s="27" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="24" t="n"/>
@@ -10040,6 +10480,8 @@
       <c r="K207" s="25" t="n"/>
       <c r="L207" s="24" t="n"/>
       <c r="M207" s="24" t="n"/>
+      <c r="N207" s="24" t="n"/>
+      <c r="O207" s="27" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="24" t="n"/>
@@ -10055,6 +10497,8 @@
       <c r="K208" s="25" t="n"/>
       <c r="L208" s="24" t="n"/>
       <c r="M208" s="24" t="n"/>
+      <c r="N208" s="24" t="n"/>
+      <c r="O208" s="27" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="24" t="n"/>
@@ -10070,6 +10514,8 @@
       <c r="K209" s="25" t="n"/>
       <c r="L209" s="24" t="n"/>
       <c r="M209" s="24" t="n"/>
+      <c r="N209" s="24" t="n"/>
+      <c r="O209" s="27" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="24" t="n"/>
@@ -10085,6 +10531,8 @@
       <c r="K210" s="25" t="n"/>
       <c r="L210" s="24" t="n"/>
       <c r="M210" s="24" t="n"/>
+      <c r="N210" s="24" t="n"/>
+      <c r="O210" s="27" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="24" t="n"/>
@@ -10100,6 +10548,8 @@
       <c r="K211" s="25" t="n"/>
       <c r="L211" s="24" t="n"/>
       <c r="M211" s="24" t="n"/>
+      <c r="N211" s="24" t="n"/>
+      <c r="O211" s="27" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="24" t="n"/>
@@ -10115,6 +10565,8 @@
       <c r="K212" s="25" t="n"/>
       <c r="L212" s="24" t="n"/>
       <c r="M212" s="24" t="n"/>
+      <c r="N212" s="24" t="n"/>
+      <c r="O212" s="27" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="24" t="n"/>
@@ -10130,6 +10582,8 @@
       <c r="K213" s="25" t="n"/>
       <c r="L213" s="24" t="n"/>
       <c r="M213" s="24" t="n"/>
+      <c r="N213" s="24" t="n"/>
+      <c r="O213" s="27" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="24" t="n"/>
@@ -10145,6 +10599,8 @@
       <c r="K214" s="25" t="n"/>
       <c r="L214" s="24" t="n"/>
       <c r="M214" s="24" t="n"/>
+      <c r="N214" s="24" t="n"/>
+      <c r="O214" s="27" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="24" t="n"/>
@@ -10160,6 +10616,8 @@
       <c r="K215" s="25" t="n"/>
       <c r="L215" s="24" t="n"/>
       <c r="M215" s="24" t="n"/>
+      <c r="N215" s="24" t="n"/>
+      <c r="O215" s="27" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="24" t="n"/>
@@ -10175,6 +10633,8 @@
       <c r="K216" s="25" t="n"/>
       <c r="L216" s="24" t="n"/>
       <c r="M216" s="24" t="n"/>
+      <c r="N216" s="24" t="n"/>
+      <c r="O216" s="27" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="24" t="n"/>
@@ -10190,6 +10650,8 @@
       <c r="K217" s="25" t="n"/>
       <c r="L217" s="24" t="n"/>
       <c r="M217" s="24" t="n"/>
+      <c r="N217" s="24" t="n"/>
+      <c r="O217" s="27" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="24" t="n"/>
@@ -10205,6 +10667,8 @@
       <c r="K218" s="25" t="n"/>
       <c r="L218" s="24" t="n"/>
       <c r="M218" s="24" t="n"/>
+      <c r="N218" s="24" t="n"/>
+      <c r="O218" s="27" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="24" t="n"/>
@@ -10220,6 +10684,8 @@
       <c r="K219" s="25" t="n"/>
       <c r="L219" s="24" t="n"/>
       <c r="M219" s="24" t="n"/>
+      <c r="N219" s="24" t="n"/>
+      <c r="O219" s="27" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="24" t="n"/>
@@ -10235,6 +10701,8 @@
       <c r="K220" s="25" t="n"/>
       <c r="L220" s="24" t="n"/>
       <c r="M220" s="24" t="n"/>
+      <c r="N220" s="24" t="n"/>
+      <c r="O220" s="27" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="24" t="n"/>
@@ -10250,6 +10718,8 @@
       <c r="K221" s="25" t="n"/>
       <c r="L221" s="24" t="n"/>
       <c r="M221" s="24" t="n"/>
+      <c r="N221" s="24" t="n"/>
+      <c r="O221" s="27" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="24" t="n"/>
@@ -10265,6 +10735,8 @@
       <c r="K222" s="25" t="n"/>
       <c r="L222" s="24" t="n"/>
       <c r="M222" s="24" t="n"/>
+      <c r="N222" s="24" t="n"/>
+      <c r="O222" s="27" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="24" t="n"/>
@@ -10280,6 +10752,8 @@
       <c r="K223" s="25" t="n"/>
       <c r="L223" s="24" t="n"/>
       <c r="M223" s="24" t="n"/>
+      <c r="N223" s="24" t="n"/>
+      <c r="O223" s="27" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="24" t="n"/>
@@ -10295,6 +10769,8 @@
       <c r="K224" s="25" t="n"/>
       <c r="L224" s="24" t="n"/>
       <c r="M224" s="24" t="n"/>
+      <c r="N224" s="24" t="n"/>
+      <c r="O224" s="27" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="24" t="n"/>
@@ -10310,6 +10786,8 @@
       <c r="K225" s="25" t="n"/>
       <c r="L225" s="24" t="n"/>
       <c r="M225" s="24" t="n"/>
+      <c r="N225" s="24" t="n"/>
+      <c r="O225" s="27" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="24" t="n"/>
@@ -10325,6 +10803,8 @@
       <c r="K226" s="25" t="n"/>
       <c r="L226" s="24" t="n"/>
       <c r="M226" s="24" t="n"/>
+      <c r="N226" s="24" t="n"/>
+      <c r="O226" s="27" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="24" t="n"/>
@@ -10340,6 +10820,8 @@
       <c r="K227" s="25" t="n"/>
       <c r="L227" s="24" t="n"/>
       <c r="M227" s="24" t="n"/>
+      <c r="N227" s="24" t="n"/>
+      <c r="O227" s="27" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="24" t="n"/>
@@ -10355,6 +10837,8 @@
       <c r="K228" s="25" t="n"/>
       <c r="L228" s="24" t="n"/>
       <c r="M228" s="24" t="n"/>
+      <c r="N228" s="24" t="n"/>
+      <c r="O228" s="27" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="24" t="n"/>
@@ -10370,6 +10854,8 @@
       <c r="K229" s="25" t="n"/>
       <c r="L229" s="24" t="n"/>
       <c r="M229" s="24" t="n"/>
+      <c r="N229" s="24" t="n"/>
+      <c r="O229" s="27" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="24" t="n"/>
@@ -10385,6 +10871,8 @@
       <c r="K230" s="25" t="n"/>
       <c r="L230" s="24" t="n"/>
       <c r="M230" s="24" t="n"/>
+      <c r="N230" s="24" t="n"/>
+      <c r="O230" s="27" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="24" t="n"/>
@@ -10400,6 +10888,8 @@
       <c r="K231" s="25" t="n"/>
       <c r="L231" s="24" t="n"/>
       <c r="M231" s="24" t="n"/>
+      <c r="N231" s="24" t="n"/>
+      <c r="O231" s="27" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="24" t="n"/>
@@ -10415,6 +10905,8 @@
       <c r="K232" s="25" t="n"/>
       <c r="L232" s="24" t="n"/>
       <c r="M232" s="24" t="n"/>
+      <c r="N232" s="24" t="n"/>
+      <c r="O232" s="27" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="24" t="n"/>
@@ -10430,6 +10922,8 @@
       <c r="K233" s="25" t="n"/>
       <c r="L233" s="24" t="n"/>
       <c r="M233" s="24" t="n"/>
+      <c r="N233" s="24" t="n"/>
+      <c r="O233" s="27" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="24" t="n"/>
@@ -10445,6 +10939,8 @@
       <c r="K234" s="25" t="n"/>
       <c r="L234" s="24" t="n"/>
       <c r="M234" s="24" t="n"/>
+      <c r="N234" s="24" t="n"/>
+      <c r="O234" s="27" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="24" t="n"/>
@@ -10460,6 +10956,8 @@
       <c r="K235" s="25" t="n"/>
       <c r="L235" s="24" t="n"/>
       <c r="M235" s="24" t="n"/>
+      <c r="N235" s="24" t="n"/>
+      <c r="O235" s="27" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="24" t="n"/>
@@ -10475,6 +10973,8 @@
       <c r="K236" s="25" t="n"/>
       <c r="L236" s="24" t="n"/>
       <c r="M236" s="24" t="n"/>
+      <c r="N236" s="24" t="n"/>
+      <c r="O236" s="27" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="24" t="n"/>
@@ -10490,6 +10990,8 @@
       <c r="K237" s="25" t="n"/>
       <c r="L237" s="24" t="n"/>
       <c r="M237" s="24" t="n"/>
+      <c r="N237" s="24" t="n"/>
+      <c r="O237" s="27" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="24" t="n"/>
@@ -10505,6 +11007,8 @@
       <c r="K238" s="25" t="n"/>
       <c r="L238" s="24" t="n"/>
       <c r="M238" s="24" t="n"/>
+      <c r="N238" s="24" t="n"/>
+      <c r="O238" s="27" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="24" t="n"/>
@@ -10520,6 +11024,8 @@
       <c r="K239" s="25" t="n"/>
       <c r="L239" s="24" t="n"/>
       <c r="M239" s="24" t="n"/>
+      <c r="N239" s="24" t="n"/>
+      <c r="O239" s="27" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="24" t="n"/>
@@ -10535,6 +11041,8 @@
       <c r="K240" s="25" t="n"/>
       <c r="L240" s="24" t="n"/>
       <c r="M240" s="24" t="n"/>
+      <c r="N240" s="24" t="n"/>
+      <c r="O240" s="27" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="24" t="n"/>
@@ -10550,6 +11058,8 @@
       <c r="K241" s="25" t="n"/>
       <c r="L241" s="24" t="n"/>
       <c r="M241" s="24" t="n"/>
+      <c r="N241" s="24" t="n"/>
+      <c r="O241" s="27" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="24" t="n"/>
@@ -10565,6 +11075,8 @@
       <c r="K242" s="25" t="n"/>
       <c r="L242" s="24" t="n"/>
       <c r="M242" s="24" t="n"/>
+      <c r="N242" s="24" t="n"/>
+      <c r="O242" s="27" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="24" t="n"/>
@@ -10580,6 +11092,8 @@
       <c r="K243" s="25" t="n"/>
       <c r="L243" s="24" t="n"/>
       <c r="M243" s="24" t="n"/>
+      <c r="N243" s="24" t="n"/>
+      <c r="O243" s="27" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="24" t="n"/>
@@ -10595,6 +11109,8 @@
       <c r="K244" s="25" t="n"/>
       <c r="L244" s="24" t="n"/>
       <c r="M244" s="24" t="n"/>
+      <c r="N244" s="24" t="n"/>
+      <c r="O244" s="27" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="24" t="n"/>
@@ -10610,6 +11126,8 @@
       <c r="K245" s="25" t="n"/>
       <c r="L245" s="24" t="n"/>
       <c r="M245" s="24" t="n"/>
+      <c r="N245" s="24" t="n"/>
+      <c r="O245" s="27" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="24" t="n"/>
@@ -10625,6 +11143,8 @@
       <c r="K246" s="25" t="n"/>
       <c r="L246" s="24" t="n"/>
       <c r="M246" s="24" t="n"/>
+      <c r="N246" s="24" t="n"/>
+      <c r="O246" s="27" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="24" t="n"/>
@@ -10640,6 +11160,8 @@
       <c r="K247" s="25" t="n"/>
       <c r="L247" s="24" t="n"/>
       <c r="M247" s="24" t="n"/>
+      <c r="N247" s="24" t="n"/>
+      <c r="O247" s="27" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="24" t="n"/>
@@ -10655,6 +11177,8 @@
       <c r="K248" s="25" t="n"/>
       <c r="L248" s="24" t="n"/>
       <c r="M248" s="24" t="n"/>
+      <c r="N248" s="24" t="n"/>
+      <c r="O248" s="27" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="24" t="n"/>
@@ -10670,6 +11194,8 @@
       <c r="K249" s="25" t="n"/>
       <c r="L249" s="24" t="n"/>
       <c r="M249" s="24" t="n"/>
+      <c r="N249" s="24" t="n"/>
+      <c r="O249" s="27" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="24" t="n"/>
@@ -10685,6 +11211,8 @@
       <c r="K250" s="25" t="n"/>
       <c r="L250" s="24" t="n"/>
       <c r="M250" s="24" t="n"/>
+      <c r="N250" s="24" t="n"/>
+      <c r="O250" s="27" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="24" t="n"/>
@@ -10700,6 +11228,8 @@
       <c r="K251" s="25" t="n"/>
       <c r="L251" s="24" t="n"/>
       <c r="M251" s="24" t="n"/>
+      <c r="N251" s="24" t="n"/>
+      <c r="O251" s="27" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="24" t="n"/>
@@ -10715,6 +11245,8 @@
       <c r="K252" s="25" t="n"/>
       <c r="L252" s="24" t="n"/>
       <c r="M252" s="24" t="n"/>
+      <c r="N252" s="24" t="n"/>
+      <c r="O252" s="27" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="24" t="n"/>
@@ -10730,6 +11262,8 @@
       <c r="K253" s="25" t="n"/>
       <c r="L253" s="24" t="n"/>
       <c r="M253" s="24" t="n"/>
+      <c r="N253" s="24" t="n"/>
+      <c r="O253" s="27" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="24" t="n"/>
@@ -10745,15 +11279,22 @@
       <c r="K254" s="25" t="n"/>
       <c r="L254" s="24" t="n"/>
       <c r="M254" s="24" t="n"/>
+      <c r="N254" s="24" t="n"/>
+      <c r="O254" s="27" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:M254">
+  <conditionalFormatting sqref="A5:O254">
     <cfRule type="expression" priority="1" dxfId="2" stopIfTrue="0">
       <formula>$H5="Odmítnuto"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O254">
+    <cfRule type="expression" priority="2" dxfId="4" stopIfTrue="0">
+      <formula>$O5="Ano"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H5:H254">
-    <cfRule type="expression" priority="2" dxfId="4" stopIfTrue="0">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="0">
       <formula>$H5="Potvrzeno"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10767,7 +11308,7 @@
     <dataValidation sqref="F5:F254" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte hodnotu ze seznamu." type="list">
       <formula1>"Obřad a hostina,Jen večer,Jen oznámení"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G254 J5:J254" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte hodnotu ze seznamu." type="list">
+    <dataValidation sqref="G5:G254 J5:J254 O5:O254" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte hodnotu ze seznamu." type="list">
       <formula1>"Ano,Ne"</formula1>
     </dataValidation>
     <dataValidation sqref="H5:H254" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte hodnotu ze seznamu." type="list">
@@ -12860,7 +13401,7 @@
     <row r="8">
       <c r="B8" s="42" t="inlineStr">
         <is>
-          <t>4. Hosté: jeden řádek = jedna pozvánka. Do sloupce Osob napište, kolik lidí na ni přijde.</t>
+          <t>4. Hosté: jeden řádek = jedna pozvánka. Do sloupce Osob napište, kolik lidí na ni přijde. Po svatbě si tu zapíšete dary a komu už jste poděkovali.</t>
         </is>
       </c>
     </row>
@@ -12956,7 +13497,7 @@
     <row r="24">
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>Ano, beru · anoberu.cz · verze 1.0</t>
+          <t>Ano, beru · anoberu.cz · verze 1.1</t>
         </is>
       </c>
     </row>
